--- a/examples/08_CeO2_on_Si_65deg.xlsx
+++ b/examples/08_CeO2_on_Si_65deg.xlsx
@@ -3901,7 +3901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3971,100 +3971,112 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Угол падения, град</t>
+          <t>Задняя сторона подложки</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>65</v>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>нет (зачернена / матирована / отсечена)</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Толщина (номинал), нм</t>
+          <t>Угол падения, град</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>900</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
+          <t>Толщина (номинал), нм</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
           <t>Неопределённость толщины, %</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>±5</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Диапазон длин волн, нм</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>400 – 800, шаг 2</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Спектральная полоса прибора, нм (FWHM)</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B11" s="4" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Шумовая модель</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>столбцы σΨ, σΔ — повторяемость прибора (σΔ растёт при Ψ → 0)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Прибор</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>RCE-эллипсометр с ПЗС, все длины волн одновременно; Δ в диапазоне 0–360°; конвенция N = n − ik (Аззам–Башара)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Возможные дефекты</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>неоднородность по глубине (линейный градиент n), шероховатость поверхности (EMA-слой Бруггемана 50/50), поглощение (хвост ниже края: второй осциллятор Тауца–Лоренца с теми же E0, C и порогом E_t = 1.2 эВ; размер — k хвоста при 400 нм)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Назначение</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>тестовый файл для приложения: опорный фит однородной плёнки → ИИ по остатку → окончательный фит; истинные параметры — в answer_key.xlsx</t>
         </is>

--- a/examples/08_CeO2_on_Si_65deg.xlsx
+++ b/examples/08_CeO2_on_Si_65deg.xlsx
@@ -478,16 +478,16 @@
         <v>400</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>13.2359</v>
+        <v>13.2402</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>207.2896</v>
+        <v>208.0209</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0.035</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.1725</v>
+        <v>0.1724</v>
       </c>
     </row>
     <row r="3">
@@ -495,16 +495,16 @@
         <v>402</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>12.0345</v>
+        <v>11.9889</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>232.3186</v>
+        <v>233.2196</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0.0347</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.1863</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="4">
@@ -512,16 +512,16 @@
         <v>404</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>10.3806</v>
+        <v>10.32</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>267.2664</v>
+        <v>268.5724</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0.0344</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.2129</v>
+        <v>0.2141</v>
       </c>
     </row>
     <row r="5">
@@ -529,10 +529,10 @@
         <v>406</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>9.2925</v>
+        <v>9.2919</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>320.2419</v>
+        <v>322.4634</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0.0341</v>
@@ -546,16 +546,16 @@
         <v>408</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>10.7303</v>
+        <v>10.8881</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>24.1979</v>
+        <v>26.9364</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0.0337</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.2038</v>
+        <v>0.201</v>
       </c>
     </row>
     <row r="7">
@@ -563,16 +563,16 @@
         <v>410</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>13.5769</v>
+        <v>13.7996</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>73.3967</v>
+        <v>75.5534</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0.0334</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.1621</v>
+        <v>0.1596</v>
       </c>
     </row>
     <row r="8">
@@ -580,16 +580,16 @@
         <v>412</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>15.9287</v>
+        <v>16.1469</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>106.951</v>
+        <v>108.4695</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0.0331</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.1384</v>
+        <v>0.1367</v>
       </c>
     </row>
     <row r="9">
@@ -597,16 +597,16 @@
         <v>414</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>17.637</v>
+        <v>17.8592</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>131.3772</v>
+        <v>132.5626</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0.0328</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.1247</v>
+        <v>0.1234</v>
       </c>
     </row>
     <row r="10">
@@ -614,16 +614,16 @@
         <v>416</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>18.9178</v>
+        <v>19.1592</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>152.5413</v>
+        <v>153.5906</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>0.0325</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.1164</v>
+        <v>0.1151</v>
       </c>
     </row>
     <row r="11">
@@ -631,16 +631,16 @@
         <v>418</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>19.7469</v>
+        <v>20.0229</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>172.013</v>
+        <v>173.0416</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>0.0322</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.1116</v>
+        <v>0.1103</v>
       </c>
     </row>
     <row r="12">
@@ -648,16 +648,16 @@
         <v>420</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>19.9808</v>
+        <v>20.299</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>191.056</v>
+        <v>192.1315</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>0.0319</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.1092</v>
+        <v>0.1078</v>
       </c>
     </row>
     <row r="13">
@@ -665,16 +665,16 @@
         <v>422</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>19.9672</v>
+        <v>20.2501</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>210.5273</v>
+        <v>211.6609</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>0.0316</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.1082</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="14">
@@ -682,16 +682,16 @@
         <v>424</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>19.9825</v>
+        <v>20.248</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>231.3168</v>
+        <v>232.4968</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>0.0313</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.1078</v>
+        <v>0.1066</v>
       </c>
     </row>
     <row r="15">
@@ -699,16 +699,16 @@
         <v>426</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>19.9726</v>
+        <v>20.2608</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>254.4588</v>
+        <v>255.6638</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>0.0311</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.1064</v>
+        <v>0.1052</v>
       </c>
     </row>
     <row r="16">
@@ -716,16 +716,16 @@
         <v>428</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>20.9238</v>
+        <v>21.2937</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>281.5785</v>
+        <v>282.8221</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>0.0308</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.1014</v>
+        <v>0.0999</v>
       </c>
     </row>
     <row r="17">
@@ -733,16 +733,16 @@
         <v>430</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>23.3806</v>
+        <v>23.8824</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>316.529</v>
+        <v>318.1211</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>0.0305</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.092</v>
+        <v>0.0906</v>
       </c>
     </row>
     <row r="18">
@@ -750,16 +750,16 @@
         <v>432</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>25.5648</v>
+        <v>26.0184</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>0.9663</v>
+        <v>3.6844</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>0.0302</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.0854</v>
+        <v>0.0843</v>
       </c>
     </row>
     <row r="19">
@@ -767,16 +767,16 @@
         <v>434</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>24.3959</v>
+        <v>24.5604</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>44.5269</v>
+        <v>47.3671</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>0.0299</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.08699999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -784,16 +784,16 @@
         <v>436</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>22.4867</v>
+        <v>22.6001</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>76.89149999999999</v>
+        <v>78.92829999999999</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>0.0297</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.092</v>
       </c>
     </row>
     <row r="21">
@@ -801,16 +801,16 @@
         <v>438</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>21.5932</v>
+        <v>21.7259</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>100.7543</v>
+        <v>102.2502</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>0.0294</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.0945</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="22">
@@ -818,16 +818,16 @@
         <v>440</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>21.4299</v>
+        <v>21.5633</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>120.6879</v>
+        <v>121.9004</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>0.0291</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.0941</v>
+        <v>0.09370000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -835,16 +835,16 @@
         <v>442</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>21.618</v>
+        <v>21.7158</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>138.2191</v>
+        <v>139.3</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>0.0288</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.0927</v>
+        <v>0.0924</v>
       </c>
     </row>
     <row r="24">
@@ -852,16 +852,16 @@
         <v>444</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>21.709</v>
+        <v>21.7667</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>154.5842</v>
+        <v>155.5921</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>0.0286</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.0911</v>
       </c>
     </row>
     <row r="25">
@@ -869,10 +869,10 @@
         <v>446</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>21.7887</v>
+        <v>21.807</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>169.7996</v>
+        <v>170.7619</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>0.0283</v>
@@ -886,10 +886,10 @@
         <v>448</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>21.7877</v>
+        <v>21.7693</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>184.7716</v>
+        <v>185.7022</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>0.0281</v>
@@ -903,16 +903,16 @@
         <v>450</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>21.6016</v>
+        <v>21.5507</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>199.4756</v>
+        <v>200.3849</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>0.0278</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0.0893</v>
+        <v>0.08939999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -920,16 +920,16 @@
         <v>452</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>21.3913</v>
+        <v>21.3135</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>214.3459</v>
+        <v>215.2441</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>0.0275</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.0892</v>
+        <v>0.0895</v>
       </c>
     </row>
     <row r="29">
@@ -937,16 +937,16 @@
         <v>454</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>21.1833</v>
+        <v>21.0852</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>229.5997</v>
+        <v>230.4993</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>0.0273</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.089</v>
+        <v>0.0893</v>
       </c>
     </row>
     <row r="30">
@@ -954,16 +954,16 @@
         <v>456</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>21.2137</v>
+        <v>21.1015</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>245.3891</v>
+        <v>246.3095</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>0.027</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.0883</v>
+        <v>0.0886</v>
       </c>
     </row>
     <row r="31">
@@ -971,16 +971,16 @@
         <v>458</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>21.5632</v>
+        <v>21.4405</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>262.3555</v>
+        <v>263.3302</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>0.0268</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0.0863</v>
+        <v>0.0867</v>
       </c>
     </row>
     <row r="32">
@@ -988,16 +988,16 @@
         <v>460</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>22.5972</v>
+        <v>22.4553</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>281.5195</v>
+        <v>282.6086</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>0.0266</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0.0824</v>
+        <v>0.0828</v>
       </c>
     </row>
     <row r="33">
@@ -1005,16 +1005,16 @@
         <v>462</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>24.4533</v>
+        <v>24.2445</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>304.2971</v>
+        <v>305.6335</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>0.0263</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>0.0767</v>
+        <v>0.0772</v>
       </c>
     </row>
     <row r="34">
@@ -1022,16 +1022,16 @@
         <v>464</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>26.8088</v>
+        <v>26.4548</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>332.1402</v>
+        <v>333.8145</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>0.0261</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.0713</v>
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1039,16 +1039,16 @@
         <v>466</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>27.5788</v>
+        <v>27.0346</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>4.5983</v>
+        <v>6.4584</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>0.0258</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>0.0692</v>
+        <v>0.0701</v>
       </c>
     </row>
     <row r="36">
@@ -1056,16 +1056,16 @@
         <v>468</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>26.0979</v>
+        <v>25.503</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>35.3933</v>
+        <v>37.0089</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>0.0256</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.0712</v>
+        <v>0.07240000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1073,16 +1073,16 @@
         <v>470</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>23.8895</v>
+        <v>23.3978</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>60.3396</v>
+        <v>61.5983</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>0.0254</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.0766</v>
       </c>
     </row>
     <row r="38">
@@ -1090,16 +1090,16 @@
         <v>472</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>22.1834</v>
+        <v>21.8051</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>80.1807</v>
+        <v>81.2136</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>0.0251</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0.0791</v>
+        <v>0.08019999999999999</v>
       </c>
     </row>
     <row r="39">
@@ -1107,16 +1107,16 @@
         <v>474</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>21.1993</v>
+        <v>20.8961</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>96.8066</v>
+        <v>97.7148</v>
       </c>
       <c r="D39" s="2" t="n">
         <v>0.0249</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0.0813</v>
+        <v>0.0822</v>
       </c>
     </row>
     <row r="40">
@@ -1124,16 +1124,16 @@
         <v>476</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>20.6945</v>
+        <v>20.4348</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>111.4225</v>
+        <v>112.25</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>0.0247</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0829</v>
       </c>
     </row>
     <row r="41">
@@ -1141,16 +1141,16 @@
         <v>478</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>20.4976</v>
+        <v>20.2622</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>124.7453</v>
+        <v>125.5089</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>0.0245</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>0.082</v>
+        <v>0.0828</v>
       </c>
     </row>
     <row r="42">
@@ -1158,16 +1158,16 @@
         <v>480</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>20.4642</v>
+        <v>20.2429</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>137.5017</v>
+        <v>138.2123</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>0.0242</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0.0814</v>
+        <v>0.0822</v>
       </c>
     </row>
     <row r="43">
@@ -1175,16 +1175,16 @@
         <v>482</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>20.4608</v>
+        <v>20.2526</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>149.3616</v>
+        <v>150.0304</v>
       </c>
       <c r="D43" s="2" t="n">
         <v>0.024</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.0808</v>
+        <v>0.0814</v>
       </c>
     </row>
     <row r="44">
@@ -1192,16 +1192,16 @@
         <v>484</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>20.4084</v>
+        <v>20.2109</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>160.9273</v>
+        <v>161.5594</v>
       </c>
       <c r="D44" s="2" t="n">
         <v>0.0238</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.0801</v>
+        <v>0.08069999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1209,16 +1209,16 @@
         <v>486</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>20.3889</v>
+        <v>20.2017</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>172.219</v>
+        <v>172.8186</v>
       </c>
       <c r="D45" s="2" t="n">
         <v>0.0236</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>0.0795</v>
+        <v>0.0801</v>
       </c>
     </row>
     <row r="46">
@@ -1226,16 +1226,16 @@
         <v>488</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>20.3201</v>
+        <v>20.1444</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>183.1895</v>
+        <v>183.7607</v>
       </c>
       <c r="D46" s="2" t="n">
         <v>0.0234</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>0.079</v>
+        <v>0.0796</v>
       </c>
     </row>
     <row r="47">
@@ -1243,16 +1243,16 @@
         <v>490</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>20.2124</v>
+        <v>20.0509</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>194.433</v>
+        <v>194.9843</v>
       </c>
       <c r="D47" s="2" t="n">
         <v>0.0232</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0.0786</v>
+        <v>0.07920000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -1260,16 +1260,16 @@
         <v>492</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>20.058</v>
+        <v>19.915</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>205.3099</v>
+        <v>205.8451</v>
       </c>
       <c r="D48" s="2" t="n">
         <v>0.023</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0.0784</v>
+        <v>0.0788</v>
       </c>
     </row>
     <row r="49">
@@ -1277,16 +1277,16 @@
         <v>494</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>19.9441</v>
+        <v>19.8243</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>216.298</v>
+        <v>216.8235</v>
       </c>
       <c r="D49" s="2" t="n">
         <v>0.0228</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>0.0781</v>
+        <v>0.0785</v>
       </c>
     </row>
     <row r="50">
@@ -1294,16 +1294,16 @@
         <v>496</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>19.8486</v>
+        <v>19.7566</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>227.512</v>
+        <v>228.0332</v>
       </c>
       <c r="D50" s="2" t="n">
         <v>0.0226</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0781</v>
       </c>
     </row>
     <row r="51">
@@ -1311,16 +1311,16 @@
         <v>498</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>19.8575</v>
+        <v>19.7975</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>239.0479</v>
+        <v>239.5678</v>
       </c>
       <c r="D51" s="2" t="n">
         <v>0.0224</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>0.0772</v>
+        <v>0.07729999999999999</v>
       </c>
     </row>
     <row r="52">
@@ -1328,16 +1328,16 @@
         <v>500</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>19.9764</v>
+        <v>19.9491</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>250.9878</v>
+        <v>251.5076</v>
       </c>
       <c r="D52" s="2" t="n">
         <v>0.0222</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>0.0761</v>
+        <v>0.0762</v>
       </c>
     </row>
     <row r="53">
@@ -1345,16 +1345,16 @@
         <v>502</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>20.3155</v>
+        <v>20.2894</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>263.6259</v>
+        <v>264.1673</v>
       </c>
       <c r="D53" s="2" t="n">
         <v>0.022</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>0.0743</v>
+        <v>0.07439999999999999</v>
       </c>
     </row>
     <row r="54">
@@ -1362,16 +1362,16 @@
         <v>504</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>21.0213</v>
+        <v>20.9935</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>277.1477</v>
+        <v>277.728</v>
       </c>
       <c r="D54" s="2" t="n">
         <v>0.0218</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>0.0717</v>
+        <v>0.0718</v>
       </c>
     </row>
     <row r="55">
@@ -1379,16 +1379,16 @@
         <v>506</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>22.0743</v>
+        <v>22.0415</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>292.2465</v>
+        <v>292.8878</v>
       </c>
       <c r="D55" s="2" t="n">
         <v>0.0216</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>0.0683</v>
+        <v>0.0684</v>
       </c>
     </row>
     <row r="56">
@@ -1396,16 +1396,16 @@
         <v>508</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>23.5252</v>
+        <v>23.4788</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>309.196</v>
+        <v>309.9258</v>
       </c>
       <c r="D56" s="2" t="n">
         <v>0.0215</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0.0645</v>
+        <v>0.0646</v>
       </c>
     </row>
     <row r="57">
@@ -1413,16 +1413,16 @@
         <v>510</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>25.0443</v>
+        <v>24.969</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>328.8739</v>
+        <v>329.7171</v>
       </c>
       <c r="D57" s="2" t="n">
         <v>0.0213</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>0.0611</v>
+        <v>0.0612</v>
       </c>
     </row>
     <row r="58">
@@ -1430,16 +1430,16 @@
         <v>512</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>25.9794</v>
+        <v>25.8582</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>350.7175</v>
+        <v>351.6619</v>
       </c>
       <c r="D58" s="2" t="n">
         <v>0.0211</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>0.059</v>
+        <v>0.0592</v>
       </c>
     </row>
     <row r="59">
@@ -1447,16 +1447,16 @@
         <v>514</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>25.8042</v>
+        <v>25.6392</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>13.427</v>
+        <v>14.3885</v>
       </c>
       <c r="D59" s="2" t="n">
         <v>0.0209</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>0.0588</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="60">
@@ -1464,16 +1464,16 @@
         <v>516</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>24.6262</v>
+        <v>24.4503</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>34.3126</v>
+        <v>35.1849</v>
       </c>
       <c r="D60" s="2" t="n">
         <v>0.0207</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>0.0602</v>
+        <v>0.0606</v>
       </c>
     </row>
     <row r="61">
@@ -1481,16 +1481,16 @@
         <v>518</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>23.1189</v>
+        <v>22.9656</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>52.5393</v>
+        <v>53.2831</v>
       </c>
       <c r="D61" s="2" t="n">
         <v>0.0206</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>0.0626</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="62">
@@ -1498,16 +1498,16 @@
         <v>520</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>21.7636</v>
+        <v>21.6437</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>67.8439</v>
+        <v>68.47410000000001</v>
       </c>
       <c r="D62" s="2" t="n">
         <v>0.0204</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.0654</v>
       </c>
     </row>
     <row r="63">
@@ -1515,16 +1515,16 @@
         <v>522</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>20.767</v>
+        <v>20.6664</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>81.3935</v>
+        <v>81.9402</v>
       </c>
       <c r="D63" s="2" t="n">
         <v>0.0202</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>0.0672</v>
+        <v>0.0674</v>
       </c>
     </row>
     <row r="64">
@@ -1532,16 +1532,16 @@
         <v>524</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>20.0869</v>
+        <v>20.0016</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>93.4128</v>
+        <v>93.90179999999999</v>
       </c>
       <c r="D64" s="2" t="n">
         <v>0.0201</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.0688</v>
       </c>
     </row>
     <row r="65">
@@ -1549,16 +1549,16 @@
         <v>526</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>19.5824</v>
+        <v>19.5085</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>104.4612</v>
+        <v>104.9093</v>
       </c>
       <c r="D65" s="2" t="n">
         <v>0.0199</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>0.0694</v>
+        <v>0.0696</v>
       </c>
     </row>
     <row r="66">
@@ -1566,16 +1566,16 @@
         <v>528</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>19.325</v>
+        <v>19.2591</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>114.8032</v>
+        <v>115.2201</v>
       </c>
       <c r="D66" s="2" t="n">
         <v>0.0198</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>0.0697</v>
+        <v>0.0699</v>
       </c>
     </row>
     <row r="67">
@@ -1583,16 +1583,16 @@
         <v>530</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>19.1461</v>
+        <v>19.0854</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>124.543</v>
+        <v>124.934</v>
       </c>
       <c r="D67" s="2" t="n">
         <v>0.0196</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>0.0697</v>
+        <v>0.0699</v>
       </c>
     </row>
     <row r="68">
@@ -1600,16 +1600,16 @@
         <v>532</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>19.008</v>
+        <v>18.9505</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>133.7262</v>
+        <v>134.0942</v>
       </c>
       <c r="D68" s="2" t="n">
         <v>0.0195</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>0.0694</v>
+        <v>0.0696</v>
       </c>
     </row>
     <row r="69">
@@ -1617,16 +1617,16 @@
         <v>534</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>18.9375</v>
+        <v>18.8825</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>142.798</v>
+        <v>143.1459</v>
       </c>
       <c r="D69" s="2" t="n">
         <v>0.0193</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0692</v>
       </c>
     </row>
     <row r="70">
@@ -1634,16 +1634,16 @@
         <v>536</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>18.9707</v>
+        <v>18.9177</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>151.6117</v>
+        <v>151.9411</v>
       </c>
       <c r="D70" s="2" t="n">
         <v>0.0192</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.0688</v>
       </c>
     </row>
     <row r="71">
@@ -1651,16 +1651,16 @@
         <v>538</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>18.9015</v>
+        <v>18.8508</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>160.2945</v>
+        <v>160.6069</v>
       </c>
       <c r="D71" s="2" t="n">
         <v>0.019</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>0.0682</v>
+        <v>0.0684</v>
       </c>
     </row>
     <row r="72">
@@ -1668,16 +1668,16 @@
         <v>540</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>18.8951</v>
+        <v>18.8464</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>168.8012</v>
+        <v>169.0981</v>
       </c>
       <c r="D72" s="2" t="n">
         <v>0.0189</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>0.0678</v>
+        <v>0.0679</v>
       </c>
     </row>
     <row r="73">
@@ -1685,16 +1685,16 @@
         <v>542</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>18.8668</v>
+        <v>18.8136</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>177.0944</v>
+        <v>177.3821</v>
       </c>
       <c r="D73" s="2" t="n">
         <v>0.0187</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>0.0674</v>
+        <v>0.0675</v>
       </c>
     </row>
     <row r="74">
@@ -1702,16 +1702,16 @@
         <v>544</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>18.8441</v>
+        <v>18.7867</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>185.3169</v>
+        <v>185.5965</v>
       </c>
       <c r="D74" s="2" t="n">
         <v>0.0186</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>0.067</v>
+        <v>0.0672</v>
       </c>
     </row>
     <row r="75">
@@ -1719,16 +1719,16 @@
         <v>546</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>18.7626</v>
+        <v>18.7017</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>193.5106</v>
+        <v>193.7829</v>
       </c>
       <c r="D75" s="2" t="n">
         <v>0.0185</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.0668</v>
       </c>
     </row>
     <row r="76">
@@ -1736,16 +1736,16 @@
         <v>548</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>18.6986</v>
+        <v>18.6351</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>201.7256</v>
+        <v>201.9918</v>
       </c>
       <c r="D76" s="2" t="n">
         <v>0.0183</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>0.0663</v>
+        <v>0.0665</v>
       </c>
     </row>
     <row r="77">
@@ -1753,16 +1753,16 @@
         <v>550</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>18.7042</v>
+        <v>18.6385</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>209.9962</v>
+        <v>210.2577</v>
       </c>
       <c r="D77" s="2" t="n">
         <v>0.0182</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>0.066</v>
+        <v>0.06619999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -1770,16 +1770,16 @@
         <v>552</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>18.6348</v>
+        <v>18.5676</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>218.143</v>
+        <v>218.4011</v>
       </c>
       <c r="D78" s="2" t="n">
         <v>0.0181</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0658</v>
       </c>
     </row>
     <row r="79">
@@ -1787,16 +1787,16 @@
         <v>554</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>18.6557</v>
+        <v>18.5879</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>226.5133</v>
+        <v>226.7704</v>
       </c>
       <c r="D79" s="2" t="n">
         <v>0.0179</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.0654</v>
       </c>
     </row>
     <row r="80">
@@ -1804,16 +1804,16 @@
         <v>556</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>18.7009</v>
+        <v>18.6332</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>234.8861</v>
+        <v>235.1435</v>
       </c>
       <c r="D80" s="2" t="n">
         <v>0.0178</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>0.0646</v>
+        <v>0.0648</v>
       </c>
     </row>
     <row r="81">
@@ -1821,16 +1821,16 @@
         <v>558</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>18.7868</v>
+        <v>18.7196</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>243.5371</v>
+        <v>243.797</v>
       </c>
       <c r="D81" s="2" t="n">
         <v>0.0177</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>0.0639</v>
+        <v>0.0641</v>
       </c>
     </row>
     <row r="82">
@@ -1838,16 +1838,16 @@
         <v>560</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>18.9668</v>
+        <v>18.8999</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>252.1359</v>
+        <v>252.399</v>
       </c>
       <c r="D82" s="2" t="n">
         <v>0.0176</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>0.063</v>
+        <v>0.06320000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -1855,16 +1855,16 @@
         <v>562</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>19.2616</v>
+        <v>19.1918</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>261.291</v>
+        <v>261.5604</v>
       </c>
       <c r="D83" s="2" t="n">
         <v>0.0175</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>0.0617</v>
+        <v>0.0619</v>
       </c>
     </row>
     <row r="84">
@@ -1872,16 +1872,16 @@
         <v>564</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>19.6996</v>
+        <v>19.6257</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>270.8269</v>
+        <v>271.1054</v>
       </c>
       <c r="D84" s="2" t="n">
         <v>0.0174</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>0.0602</v>
+        <v>0.0604</v>
       </c>
     </row>
     <row r="85">
@@ -1889,16 +1889,16 @@
         <v>566</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>20.2807</v>
+        <v>20.2013</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>280.7386</v>
+        <v>281.0282</v>
       </c>
       <c r="D85" s="2" t="n">
         <v>0.0173</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>0.0584</v>
+        <v>0.0586</v>
       </c>
     </row>
     <row r="86">
@@ -1906,16 +1906,16 @@
         <v>568</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>21.0352</v>
+        <v>20.9484</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>291.42</v>
+        <v>291.7229</v>
       </c>
       <c r="D86" s="2" t="n">
         <v>0.0172</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>0.0563</v>
+        <v>0.0565</v>
       </c>
     </row>
     <row r="87">
@@ -1923,16 +1923,16 @@
         <v>570</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>21.988</v>
+        <v>21.8918</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>303.1497</v>
+        <v>303.4671</v>
       </c>
       <c r="D87" s="2" t="n">
         <v>0.017</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>0.054</v>
+        <v>0.0542</v>
       </c>
     </row>
     <row r="88">
@@ -1940,16 +1940,16 @@
         <v>572</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>23.0126</v>
+        <v>22.9054</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>315.8701</v>
+        <v>316.2003</v>
       </c>
       <c r="D88" s="2" t="n">
         <v>0.0169</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>0.0518</v>
+        <v>0.052</v>
       </c>
     </row>
     <row r="89">
@@ -1957,16 +1957,16 @@
         <v>574</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>23.9744</v>
+        <v>23.856</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>329.8235</v>
+        <v>330.1625</v>
       </c>
       <c r="D89" s="2" t="n">
         <v>0.0168</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>0.0499</v>
+        <v>0.0501</v>
       </c>
     </row>
     <row r="90">
@@ -1974,16 +1974,16 @@
         <v>576</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>24.6799</v>
+        <v>24.5533</v>
       </c>
       <c r="C90" s="2" t="n">
-        <v>344.7631</v>
+        <v>345.1042</v>
       </c>
       <c r="D90" s="2" t="n">
         <v>0.0168</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>0.0486</v>
+        <v>0.0488</v>
       </c>
     </row>
     <row r="91">
@@ -1991,16 +1991,16 @@
         <v>578</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>24.924</v>
+        <v>24.795</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>0.424</v>
+        <v>0.7577</v>
       </c>
       <c r="D91" s="2" t="n">
         <v>0.0167</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>0.048</v>
+        <v>0.0482</v>
       </c>
     </row>
     <row r="92">
@@ -2008,16 +2008,16 @@
         <v>580</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>24.5868</v>
+        <v>24.4631</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>15.7945</v>
+        <v>16.1083</v>
       </c>
       <c r="D92" s="2" t="n">
         <v>0.0166</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>0.0482</v>
+        <v>0.0484</v>
       </c>
     </row>
     <row r="93">
@@ -2025,16 +2025,16 @@
         <v>582</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>23.8301</v>
+        <v>23.7147</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>30.305</v>
+        <v>30.593</v>
       </c>
       <c r="D93" s="2" t="n">
         <v>0.0165</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>0.0491</v>
+        <v>0.0492</v>
       </c>
     </row>
     <row r="94">
@@ -2042,16 +2042,16 @@
         <v>584</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>22.8797</v>
+        <v>22.7789</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>43.4803</v>
+        <v>43.7378</v>
       </c>
       <c r="D94" s="2" t="n">
         <v>0.0164</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>0.0504</v>
+        <v>0.0506</v>
       </c>
     </row>
     <row r="95">
@@ -2059,16 +2059,16 @@
         <v>586</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>21.8761</v>
+        <v>21.7927</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>55.4159</v>
+        <v>55.6445</v>
       </c>
       <c r="D95" s="2" t="n">
         <v>0.0163</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>0.0519</v>
+        <v>0.0521</v>
       </c>
     </row>
     <row r="96">
@@ -2076,16 +2076,16 @@
         <v>588</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>20.9492</v>
+        <v>20.883</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>66.1932</v>
+        <v>66.3974</v>
       </c>
       <c r="D96" s="2" t="n">
         <v>0.0162</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>0.0535</v>
+        <v>0.0536</v>
       </c>
     </row>
     <row r="97">
@@ -2093,16 +2093,16 @@
         <v>590</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>20.1853</v>
+        <v>20.1348</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>75.8318</v>
+        <v>76.0153</v>
       </c>
       <c r="D97" s="2" t="n">
         <v>0.0162</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>0.0549</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="98">
@@ -2110,16 +2110,16 @@
         <v>592</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>19.5574</v>
+        <v>19.5207</v>
       </c>
       <c r="C98" s="2" t="n">
-        <v>84.9053</v>
+        <v>85.0716</v>
       </c>
       <c r="D98" s="2" t="n">
         <v>0.0161</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>0.0561</v>
+        <v>0.0562</v>
       </c>
     </row>
     <row r="99">
@@ -2127,16 +2127,16 @@
         <v>594</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>19.0514</v>
+        <v>19.0269</v>
       </c>
       <c r="C99" s="2" t="n">
-        <v>93.3536</v>
+        <v>93.50449999999999</v>
       </c>
       <c r="D99" s="2" t="n">
         <v>0.016</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>0.057</v>
+        <v>0.0571</v>
       </c>
     </row>
     <row r="100">
@@ -2144,10 +2144,10 @@
         <v>596</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>18.6502</v>
+        <v>18.6366</v>
       </c>
       <c r="C100" s="2" t="n">
-        <v>101.1737</v>
+        <v>101.3102</v>
       </c>
       <c r="D100" s="2" t="n">
         <v>0.0159</v>
@@ -2161,10 +2161,10 @@
         <v>598</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>18.404</v>
+        <v>18.4001</v>
       </c>
       <c r="C101" s="2" t="n">
-        <v>108.7152</v>
+        <v>108.8385</v>
       </c>
       <c r="D101" s="2" t="n">
         <v>0.0159</v>
@@ -2178,10 +2178,10 @@
         <v>600</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>18.1702</v>
+        <v>18.1734</v>
       </c>
       <c r="C102" s="2" t="n">
-        <v>116.1125</v>
+        <v>116.2236</v>
       </c>
       <c r="D102" s="2" t="n">
         <v>0.0158</v>
@@ -2195,10 +2195,10 @@
         <v>602</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>18.0316</v>
+        <v>18.0258</v>
       </c>
       <c r="C103" s="2" t="n">
-        <v>123.0836</v>
+        <v>123.1851</v>
       </c>
       <c r="D103" s="2" t="n">
         <v>0.0157</v>
@@ -2212,10 +2212,10 @@
         <v>604</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>17.9652</v>
+        <v>17.9494</v>
       </c>
       <c r="C104" s="2" t="n">
-        <v>130.0763</v>
+        <v>130.1712</v>
       </c>
       <c r="D104" s="2" t="n">
         <v>0.0157</v>
@@ -2229,16 +2229,16 @@
         <v>606</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>17.8549</v>
+        <v>17.8298</v>
       </c>
       <c r="C105" s="2" t="n">
-        <v>136.6204</v>
+        <v>136.71</v>
       </c>
       <c r="D105" s="2" t="n">
         <v>0.0156</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>0.0588</v>
+        <v>0.0589</v>
       </c>
     </row>
     <row r="106">
@@ -2246,16 +2246,16 @@
         <v>608</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>17.8334</v>
+        <v>17.7993</v>
       </c>
       <c r="C106" s="2" t="n">
-        <v>143.127</v>
+        <v>143.2121</v>
       </c>
       <c r="D106" s="2" t="n">
         <v>0.0156</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>0.0588</v>
+        <v>0.0589</v>
       </c>
     </row>
     <row r="107">
@@ -2263,16 +2263,16 @@
         <v>610</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>17.7713</v>
+        <v>17.729</v>
       </c>
       <c r="C107" s="2" t="n">
-        <v>149.5279</v>
+        <v>149.6084</v>
       </c>
       <c r="D107" s="2" t="n">
         <v>0.0155</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>0.0587</v>
+        <v>0.0588</v>
       </c>
     </row>
     <row r="108">
@@ -2280,16 +2280,16 @@
         <v>612</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>17.7493</v>
+        <v>17.6994</v>
       </c>
       <c r="C108" s="2" t="n">
-        <v>155.8633</v>
+        <v>155.9389</v>
       </c>
       <c r="D108" s="2" t="n">
         <v>0.0155</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>0.0586</v>
+        <v>0.0587</v>
       </c>
     </row>
     <row r="109">
@@ -2297,16 +2297,16 @@
         <v>614</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>17.7311</v>
+        <v>17.6742</v>
       </c>
       <c r="C109" s="2" t="n">
-        <v>162.0828</v>
+        <v>162.1532</v>
       </c>
       <c r="D109" s="2" t="n">
         <v>0.0154</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>0.0585</v>
+        <v>0.0586</v>
       </c>
     </row>
     <row r="110">
@@ -2314,16 +2314,16 @@
         <v>616</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>17.6876</v>
+        <v>17.624</v>
       </c>
       <c r="C110" s="2" t="n">
-        <v>168.2281</v>
+        <v>168.2929</v>
       </c>
       <c r="D110" s="2" t="n">
         <v>0.0154</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>0.0584</v>
+        <v>0.0586</v>
       </c>
     </row>
     <row r="111">
@@ -2331,16 +2331,16 @@
         <v>618</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>17.677</v>
+        <v>17.607</v>
       </c>
       <c r="C111" s="2" t="n">
-        <v>174.2566</v>
+        <v>174.3156</v>
       </c>
       <c r="D111" s="2" t="n">
         <v>0.0153</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>0.0583</v>
+        <v>0.0585</v>
       </c>
     </row>
     <row r="112">
@@ -2348,16 +2348,16 @@
         <v>620</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>17.6994</v>
+        <v>17.6236</v>
       </c>
       <c r="C112" s="2" t="n">
-        <v>180.3515</v>
+        <v>180.4053</v>
       </c>
       <c r="D112" s="2" t="n">
         <v>0.0153</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>0.0582</v>
+        <v>0.0584</v>
       </c>
     </row>
     <row r="113">
@@ -2365,16 +2365,16 @@
         <v>622</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>17.634</v>
+        <v>17.5583</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>186.3399</v>
+        <v>186.3905</v>
       </c>
       <c r="D113" s="2" t="n">
         <v>0.0153</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>0.0581</v>
+        <v>0.0583</v>
       </c>
     </row>
     <row r="114">
@@ -2382,16 +2382,16 @@
         <v>624</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>17.6252</v>
+        <v>17.5502</v>
       </c>
       <c r="C114" s="2" t="n">
-        <v>192.315</v>
+        <v>192.3625</v>
       </c>
       <c r="D114" s="2" t="n">
         <v>0.0152</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>0.058</v>
+        <v>0.0582</v>
       </c>
     </row>
     <row r="115">
@@ -2399,16 +2399,16 @@
         <v>626</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>17.6164</v>
+        <v>17.5423</v>
       </c>
       <c r="C115" s="2" t="n">
-        <v>198.2482</v>
+        <v>198.2928</v>
       </c>
       <c r="D115" s="2" t="n">
         <v>0.0152</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>0.058</v>
+        <v>0.0582</v>
       </c>
     </row>
     <row r="116">
@@ -2416,16 +2416,16 @@
         <v>628</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>17.5702</v>
+        <v>17.4971</v>
       </c>
       <c r="C116" s="2" t="n">
-        <v>204.2347</v>
+        <v>204.277</v>
       </c>
       <c r="D116" s="2" t="n">
         <v>0.0152</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>0.0579</v>
+        <v>0.0581</v>
       </c>
     </row>
     <row r="117">
@@ -2433,16 +2433,16 @@
         <v>630</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>17.5863</v>
+        <v>17.5144</v>
       </c>
       <c r="C117" s="2" t="n">
-        <v>210.0766</v>
+        <v>210.1165</v>
       </c>
       <c r="D117" s="2" t="n">
         <v>0.0151</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>0.0578</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="118">
@@ -2450,16 +2450,16 @@
         <v>632</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>17.5632</v>
+        <v>17.4926</v>
       </c>
       <c r="C118" s="2" t="n">
-        <v>215.991</v>
+        <v>216.0294</v>
       </c>
       <c r="D118" s="2" t="n">
         <v>0.0151</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>0.0577</v>
+        <v>0.0579</v>
       </c>
     </row>
     <row r="119">
@@ -2467,16 +2467,16 @@
         <v>634</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>17.5901</v>
+        <v>17.521</v>
       </c>
       <c r="C119" s="2" t="n">
-        <v>221.9551</v>
+        <v>221.9926</v>
       </c>
       <c r="D119" s="2" t="n">
         <v>0.0151</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>0.0576</v>
+        <v>0.0578</v>
       </c>
     </row>
     <row r="120">
@@ -2484,16 +2484,16 @@
         <v>636</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>17.6296</v>
+        <v>17.5622</v>
       </c>
       <c r="C120" s="2" t="n">
-        <v>227.9557</v>
+        <v>227.9927</v>
       </c>
       <c r="D120" s="2" t="n">
         <v>0.0151</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>0.0574</v>
+        <v>0.0576</v>
       </c>
     </row>
     <row r="121">
@@ -2501,16 +2501,16 @@
         <v>638</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>17.6936</v>
+        <v>17.6281</v>
       </c>
       <c r="C121" s="2" t="n">
-        <v>234.1246</v>
+        <v>234.162</v>
       </c>
       <c r="D121" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>0.0572</v>
+        <v>0.0574</v>
       </c>
     </row>
     <row r="122">
@@ -2518,16 +2518,16 @@
         <v>640</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>17.7494</v>
+        <v>17.6851</v>
       </c>
       <c r="C122" s="2" t="n">
-        <v>240.0097</v>
+        <v>240.0469</v>
       </c>
       <c r="D122" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>0.0569</v>
+        <v>0.0571</v>
       </c>
     </row>
     <row r="123">
@@ -2535,16 +2535,16 @@
         <v>642</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>17.8726</v>
+        <v>17.8036</v>
       </c>
       <c r="C123" s="2" t="n">
-        <v>246.1758</v>
+        <v>246.217</v>
       </c>
       <c r="D123" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>0.0566</v>
+        <v>0.0567</v>
       </c>
     </row>
     <row r="124">
@@ -2552,16 +2552,16 @@
         <v>644</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>18.0409</v>
+        <v>17.9665</v>
       </c>
       <c r="C124" s="2" t="n">
-        <v>252.424</v>
+        <v>252.4706</v>
       </c>
       <c r="D124" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>0.0561</v>
+        <v>0.0563</v>
       </c>
     </row>
     <row r="125">
@@ -2569,16 +2569,16 @@
         <v>646</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>18.246</v>
+        <v>18.1656</v>
       </c>
       <c r="C125" s="2" t="n">
-        <v>258.8523</v>
+        <v>258.9058</v>
       </c>
       <c r="D125" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>0.0555</v>
+        <v>0.0557</v>
       </c>
     </row>
     <row r="126">
@@ -2586,16 +2586,16 @@
         <v>648</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>18.5566</v>
+        <v>18.4697</v>
       </c>
       <c r="C126" s="2" t="n">
-        <v>265.2771</v>
+        <v>265.3382</v>
       </c>
       <c r="D126" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>0.0547</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="127">
@@ -2603,16 +2603,16 @@
         <v>650</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>18.8895</v>
+        <v>18.7953</v>
       </c>
       <c r="C127" s="2" t="n">
-        <v>271.9456</v>
+        <v>272.0158</v>
       </c>
       <c r="D127" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>0.0539</v>
+        <v>0.0541</v>
       </c>
     </row>
     <row r="128">
@@ -2620,16 +2620,16 @@
         <v>652</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>19.2903</v>
+        <v>19.1876</v>
       </c>
       <c r="C128" s="2" t="n">
-        <v>278.8581</v>
+        <v>278.9381</v>
       </c>
       <c r="D128" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>0.0529</v>
+        <v>0.0531</v>
       </c>
     </row>
     <row r="129">
@@ -2637,16 +2637,16 @@
         <v>654</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>19.7784</v>
+        <v>19.6661</v>
       </c>
       <c r="C129" s="2" t="n">
-        <v>286.0642</v>
+        <v>286.1545</v>
       </c>
       <c r="D129" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>0.0518</v>
+        <v>0.0521</v>
       </c>
     </row>
     <row r="130">
@@ -2654,16 +2654,16 @@
         <v>656</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>20.3491</v>
+        <v>20.2256</v>
       </c>
       <c r="C130" s="2" t="n">
-        <v>293.5845</v>
+        <v>293.6846</v>
       </c>
       <c r="D130" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>0.0506</v>
+        <v>0.0509</v>
       </c>
     </row>
     <row r="131">
@@ -2671,16 +2671,16 @@
         <v>658</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>20.9771</v>
+        <v>20.8409</v>
       </c>
       <c r="C131" s="2" t="n">
-        <v>301.5851</v>
+        <v>301.6936</v>
       </c>
       <c r="D131" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>0.0494</v>
+        <v>0.0496</v>
       </c>
     </row>
     <row r="132">
@@ -2688,16 +2688,16 @@
         <v>660</v>
       </c>
       <c r="B132" s="2" t="n">
-        <v>21.6609</v>
+        <v>21.5107</v>
       </c>
       <c r="C132" s="2" t="n">
-        <v>309.8366</v>
+        <v>309.9492</v>
       </c>
       <c r="D132" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>0.0481</v>
+        <v>0.0484</v>
       </c>
     </row>
     <row r="133">
@@ -2705,16 +2705,16 @@
         <v>662</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>22.3783</v>
+        <v>22.2135</v>
       </c>
       <c r="C133" s="2" t="n">
-        <v>318.847</v>
+        <v>318.96</v>
       </c>
       <c r="D133" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>0.0469</v>
+        <v>0.0472</v>
       </c>
     </row>
     <row r="134">
@@ -2722,16 +2722,16 @@
         <v>664</v>
       </c>
       <c r="B134" s="2" t="n">
-        <v>22.9809</v>
+        <v>22.8022</v>
       </c>
       <c r="C134" s="2" t="n">
-        <v>328.2972</v>
+        <v>328.4039</v>
       </c>
       <c r="D134" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>0.0459</v>
+        <v>0.0462</v>
       </c>
     </row>
     <row r="135">
@@ -2739,16 +2739,16 @@
         <v>666</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>23.487</v>
+        <v>23.2962</v>
       </c>
       <c r="C135" s="2" t="n">
-        <v>338.2135</v>
+        <v>338.3074</v>
       </c>
       <c r="D135" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>0.0451</v>
+        <v>0.0454</v>
       </c>
     </row>
     <row r="136">
@@ -2756,16 +2756,16 @@
         <v>668</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>23.8475</v>
+        <v>23.6481</v>
       </c>
       <c r="C136" s="2" t="n">
-        <v>348.5202</v>
+        <v>348.5961</v>
       </c>
       <c r="D136" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>0.0446</v>
+        <v>0.0449</v>
       </c>
     </row>
     <row r="137">
@@ -2773,16 +2773,16 @@
         <v>670</v>
       </c>
       <c r="B137" s="2" t="n">
-        <v>24.0147</v>
+        <v>23.8111</v>
       </c>
       <c r="C137" s="2" t="n">
-        <v>358.9721</v>
+        <v>359.026</v>
       </c>
       <c r="D137" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>0.0444</v>
+        <v>0.0447</v>
       </c>
     </row>
     <row r="138">
@@ -2790,16 +2790,16 @@
         <v>672</v>
       </c>
       <c r="B138" s="2" t="n">
-        <v>23.8966</v>
+        <v>23.6937</v>
       </c>
       <c r="C138" s="2" t="n">
-        <v>9.4442</v>
+        <v>9.4757</v>
       </c>
       <c r="D138" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>0.0446</v>
+        <v>0.0449</v>
       </c>
     </row>
     <row r="139">
@@ -2807,16 +2807,16 @@
         <v>674</v>
       </c>
       <c r="B139" s="2" t="n">
-        <v>23.5226</v>
+        <v>23.3253</v>
       </c>
       <c r="C139" s="2" t="n">
-        <v>19.4729</v>
+        <v>19.4823</v>
       </c>
       <c r="D139" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>0.0451</v>
+        <v>0.0454</v>
       </c>
     </row>
     <row r="140">
@@ -2824,16 +2824,16 @@
         <v>676</v>
       </c>
       <c r="B140" s="2" t="n">
-        <v>23.0565</v>
+        <v>22.8686</v>
       </c>
       <c r="C140" s="2" t="n">
-        <v>29.1562</v>
+        <v>29.1476</v>
       </c>
       <c r="D140" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>0.0458</v>
+        <v>0.0461</v>
       </c>
     </row>
     <row r="141">
@@ -2841,16 +2841,16 @@
         <v>678</v>
       </c>
       <c r="B141" s="2" t="n">
-        <v>22.4162</v>
+        <v>22.2405</v>
       </c>
       <c r="C141" s="2" t="n">
-        <v>38.1633</v>
+        <v>38.1408</v>
       </c>
       <c r="D141" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>0.0468</v>
+        <v>0.0471</v>
       </c>
     </row>
     <row r="142">
@@ -2858,16 +2858,16 @@
         <v>680</v>
       </c>
       <c r="B142" s="2" t="n">
-        <v>21.7765</v>
+        <v>21.615</v>
       </c>
       <c r="C142" s="2" t="n">
-        <v>46.6915</v>
+        <v>46.6615</v>
       </c>
       <c r="D142" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>0.0479</v>
+        <v>0.0482</v>
       </c>
     </row>
     <row r="143">
@@ -2875,16 +2875,16 @@
         <v>682</v>
       </c>
       <c r="B143" s="2" t="n">
-        <v>21.0876</v>
+        <v>20.9451</v>
       </c>
       <c r="C143" s="2" t="n">
-        <v>54.5889</v>
+        <v>54.5589</v>
       </c>
       <c r="D143" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>0.0491</v>
+        <v>0.0494</v>
       </c>
     </row>
     <row r="144">
@@ -2892,16 +2892,16 @@
         <v>684</v>
       </c>
       <c r="B144" s="2" t="n">
-        <v>20.4819</v>
+        <v>20.3571</v>
       </c>
       <c r="C144" s="2" t="n">
-        <v>61.9871</v>
+        <v>61.9606</v>
       </c>
       <c r="D144" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>0.0504</v>
+        <v>0.0506</v>
       </c>
     </row>
     <row r="145">
@@ -2909,16 +2909,16 @@
         <v>686</v>
       </c>
       <c r="B145" s="2" t="n">
-        <v>19.9335</v>
+        <v>19.8246</v>
       </c>
       <c r="C145" s="2" t="n">
-        <v>68.9028</v>
+        <v>68.88160000000001</v>
       </c>
       <c r="D145" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>0.0516</v>
+        <v>0.0518</v>
       </c>
     </row>
     <row r="146">
@@ -2926,16 +2926,16 @@
         <v>688</v>
       </c>
       <c r="B146" s="2" t="n">
-        <v>19.4172</v>
+        <v>19.3227</v>
       </c>
       <c r="C146" s="2" t="n">
-        <v>75.5031</v>
+        <v>75.4885</v>
       </c>
       <c r="D146" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>0.0527</v>
+        <v>0.0529</v>
       </c>
     </row>
     <row r="147">
@@ -2943,16 +2943,16 @@
         <v>690</v>
       </c>
       <c r="B147" s="2" t="n">
-        <v>18.9533</v>
+        <v>18.8722</v>
       </c>
       <c r="C147" s="2" t="n">
-        <v>81.6195</v>
+        <v>81.61109999999999</v>
       </c>
       <c r="D147" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>0.0537</v>
+        <v>0.0539</v>
       </c>
     </row>
     <row r="148">
@@ -2960,16 +2960,16 @@
         <v>692</v>
       </c>
       <c r="B148" s="2" t="n">
-        <v>18.561</v>
+        <v>18.493</v>
       </c>
       <c r="C148" s="2" t="n">
-        <v>87.61539999999999</v>
+        <v>87.6138</v>
       </c>
       <c r="D148" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>0.0547</v>
+        <v>0.0548</v>
       </c>
     </row>
     <row r="149">
@@ -2977,16 +2977,16 @@
         <v>694</v>
       </c>
       <c r="B149" s="2" t="n">
-        <v>18.242</v>
+        <v>18.1865</v>
       </c>
       <c r="C149" s="2" t="n">
-        <v>93.2569</v>
+        <v>93.261</v>
       </c>
       <c r="D149" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>0.0555</v>
+        <v>0.0557</v>
       </c>
     </row>
     <row r="150">
@@ -2994,16 +2994,16 @@
         <v>696</v>
       </c>
       <c r="B150" s="2" t="n">
-        <v>17.9739</v>
+        <v>17.9303</v>
       </c>
       <c r="C150" s="2" t="n">
-        <v>98.721</v>
+        <v>98.7296</v>
       </c>
       <c r="D150" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>0.0563</v>
+        <v>0.0564</v>
       </c>
     </row>
     <row r="151">
@@ -3011,16 +3011,16 @@
         <v>698</v>
       </c>
       <c r="B151" s="2" t="n">
-        <v>17.7361</v>
+        <v>17.7032</v>
       </c>
       <c r="C151" s="2" t="n">
-        <v>104.041</v>
+        <v>104.0525</v>
       </c>
       <c r="D151" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>0.0569</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="152">
@@ -3028,16 +3028,16 @@
         <v>700</v>
       </c>
       <c r="B152" s="2" t="n">
-        <v>17.5324</v>
+        <v>17.5077</v>
       </c>
       <c r="C152" s="2" t="n">
-        <v>109.107</v>
+        <v>109.1194</v>
       </c>
       <c r="D152" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E152" s="2" t="n">
-        <v>0.0575</v>
+        <v>0.0576</v>
       </c>
     </row>
     <row r="153">
@@ -3045,10 +3045,10 @@
         <v>702</v>
       </c>
       <c r="B153" s="2" t="n">
-        <v>17.3786</v>
+        <v>17.351</v>
       </c>
       <c r="C153" s="2" t="n">
-        <v>114.1349</v>
+        <v>114.1464</v>
       </c>
       <c r="D153" s="2" t="n">
         <v>0.015</v>
@@ -3062,16 +3062,16 @@
         <v>704</v>
       </c>
       <c r="B154" s="2" t="n">
-        <v>17.2319</v>
+        <v>17.2001</v>
       </c>
       <c r="C154" s="2" t="n">
-        <v>119.1164</v>
+        <v>119.1269</v>
       </c>
       <c r="D154" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E154" s="2" t="n">
-        <v>0.0583</v>
+        <v>0.0584</v>
       </c>
     </row>
     <row r="155">
@@ -3079,16 +3079,16 @@
         <v>706</v>
       </c>
       <c r="B155" s="2" t="n">
-        <v>17.1174</v>
+        <v>17.0812</v>
       </c>
       <c r="C155" s="2" t="n">
-        <v>123.9003</v>
+        <v>123.9099</v>
       </c>
       <c r="D155" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>0.0587</v>
+        <v>0.0588</v>
       </c>
     </row>
     <row r="156">
@@ -3096,16 +3096,16 @@
         <v>708</v>
       </c>
       <c r="B156" s="2" t="n">
-        <v>17.0147</v>
+        <v>16.9747</v>
       </c>
       <c r="C156" s="2" t="n">
-        <v>128.7167</v>
+        <v>128.726</v>
       </c>
       <c r="D156" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>0.0589</v>
+        <v>0.0591</v>
       </c>
     </row>
     <row r="157">
@@ -3113,16 +3113,16 @@
         <v>710</v>
       </c>
       <c r="B157" s="2" t="n">
-        <v>16.9478</v>
+        <v>16.9049</v>
       </c>
       <c r="C157" s="2" t="n">
-        <v>133.3589</v>
+        <v>133.3679</v>
       </c>
       <c r="D157" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>0.0592</v>
+        <v>0.0593</v>
       </c>
     </row>
     <row r="158">
@@ -3130,16 +3130,16 @@
         <v>712</v>
       </c>
       <c r="B158" s="2" t="n">
-        <v>16.9023</v>
+        <v>16.8575</v>
       </c>
       <c r="C158" s="2" t="n">
-        <v>137.9666</v>
+        <v>137.9755</v>
       </c>
       <c r="D158" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>0.0594</v>
+        <v>0.0595</v>
       </c>
     </row>
     <row r="159">
@@ -3147,16 +3147,16 @@
         <v>714</v>
       </c>
       <c r="B159" s="2" t="n">
-        <v>16.8044</v>
+        <v>16.7585</v>
       </c>
       <c r="C159" s="2" t="n">
-        <v>142.3722</v>
+        <v>142.3805</v>
       </c>
       <c r="D159" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>0.0595</v>
+        <v>0.0597</v>
       </c>
     </row>
     <row r="160">
@@ -3164,16 +3164,16 @@
         <v>716</v>
       </c>
       <c r="B160" s="2" t="n">
-        <v>16.8103</v>
+        <v>16.7637</v>
       </c>
       <c r="C160" s="2" t="n">
-        <v>146.9964</v>
+        <v>147.0048</v>
       </c>
       <c r="D160" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>0.0597</v>
+        <v>0.0598</v>
       </c>
     </row>
     <row r="161">
@@ -3181,16 +3181,16 @@
         <v>718</v>
       </c>
       <c r="B161" s="2" t="n">
-        <v>16.7331</v>
+        <v>16.6859</v>
       </c>
       <c r="C161" s="2" t="n">
-        <v>151.3147</v>
+        <v>151.3226</v>
       </c>
       <c r="D161" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>0.0598</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="162">
@@ -3198,16 +3198,16 @@
         <v>720</v>
       </c>
       <c r="B162" s="2" t="n">
-        <v>16.728</v>
+        <v>16.6798</v>
       </c>
       <c r="C162" s="2" t="n">
-        <v>155.8646</v>
+        <v>155.873</v>
       </c>
       <c r="D162" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>0.0599</v>
+        <v>0.0601</v>
       </c>
     </row>
     <row r="163">
@@ -3215,16 +3215,16 @@
         <v>722</v>
       </c>
       <c r="B163" s="2" t="n">
-        <v>16.7119</v>
+        <v>16.6623</v>
       </c>
       <c r="C163" s="2" t="n">
-        <v>160.1059</v>
+        <v>160.1136</v>
       </c>
       <c r="D163" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>0.06</v>
+        <v>0.0602</v>
       </c>
     </row>
     <row r="164">
@@ -3232,16 +3232,16 @@
         <v>724</v>
       </c>
       <c r="B164" s="2" t="n">
-        <v>16.664</v>
+        <v>16.613</v>
       </c>
       <c r="C164" s="2" t="n">
-        <v>164.5381</v>
+        <v>164.5461</v>
       </c>
       <c r="D164" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>0.0601</v>
+        <v>0.0602</v>
       </c>
     </row>
     <row r="165">
@@ -3249,16 +3249,16 @@
         <v>726</v>
       </c>
       <c r="B165" s="2" t="n">
-        <v>16.6374</v>
+        <v>16.585</v>
       </c>
       <c r="C165" s="2" t="n">
-        <v>168.6697</v>
+        <v>168.6773</v>
       </c>
       <c r="D165" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E165" s="2" t="n">
-        <v>0.0601</v>
+        <v>0.0603</v>
       </c>
     </row>
     <row r="166">
@@ -3266,16 +3266,16 @@
         <v>728</v>
       </c>
       <c r="B166" s="2" t="n">
-        <v>16.6438</v>
+        <v>16.59</v>
       </c>
       <c r="C166" s="2" t="n">
-        <v>172.7956</v>
+        <v>172.8029</v>
       </c>
       <c r="D166" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>0.0602</v>
+        <v>0.0604</v>
       </c>
     </row>
     <row r="167">
@@ -3283,16 +3283,16 @@
         <v>730</v>
       </c>
       <c r="B167" s="2" t="n">
-        <v>16.6117</v>
+        <v>16.557</v>
       </c>
       <c r="C167" s="2" t="n">
-        <v>177.0548</v>
+        <v>177.062</v>
       </c>
       <c r="D167" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E167" s="2" t="n">
-        <v>0.0603</v>
+        <v>0.0604</v>
       </c>
     </row>
     <row r="168">
@@ -3300,16 +3300,16 @@
         <v>732</v>
       </c>
       <c r="B168" s="2" t="n">
-        <v>16.5969</v>
+        <v>16.5417</v>
       </c>
       <c r="C168" s="2" t="n">
-        <v>181.2274</v>
+        <v>181.2341</v>
       </c>
       <c r="D168" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>0.0603</v>
+        <v>0.0605</v>
       </c>
     </row>
     <row r="169">
@@ -3317,16 +3317,16 @@
         <v>734</v>
       </c>
       <c r="B169" s="2" t="n">
-        <v>16.5687</v>
+        <v>16.5135</v>
       </c>
       <c r="C169" s="2" t="n">
-        <v>185.3963</v>
+        <v>185.4024</v>
       </c>
       <c r="D169" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>0.0603</v>
+        <v>0.0605</v>
       </c>
     </row>
     <row r="170">
@@ -3334,16 +3334,16 @@
         <v>736</v>
       </c>
       <c r="B170" s="2" t="n">
-        <v>16.5883</v>
+        <v>16.533</v>
       </c>
       <c r="C170" s="2" t="n">
-        <v>189.6385</v>
+        <v>189.6444</v>
       </c>
       <c r="D170" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E170" s="2" t="n">
-        <v>0.0604</v>
+        <v>0.0606</v>
       </c>
     </row>
     <row r="171">
@@ -3351,16 +3351,16 @@
         <v>738</v>
       </c>
       <c r="B171" s="2" t="n">
-        <v>16.5659</v>
+        <v>16.5108</v>
       </c>
       <c r="C171" s="2" t="n">
-        <v>193.8186</v>
+        <v>193.824</v>
       </c>
       <c r="D171" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E171" s="2" t="n">
-        <v>0.0604</v>
+        <v>0.0606</v>
       </c>
     </row>
     <row r="172">
@@ -3368,16 +3368,16 @@
         <v>740</v>
       </c>
       <c r="B172" s="2" t="n">
-        <v>16.5906</v>
+        <v>16.5351</v>
       </c>
       <c r="C172" s="2" t="n">
-        <v>197.7544</v>
+        <v>197.7588</v>
       </c>
       <c r="D172" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E172" s="2" t="n">
-        <v>0.0604</v>
+        <v>0.0606</v>
       </c>
     </row>
     <row r="173">
@@ -3385,16 +3385,16 @@
         <v>742</v>
       </c>
       <c r="B173" s="2" t="n">
-        <v>16.5888</v>
+        <v>16.5296</v>
       </c>
       <c r="C173" s="2" t="n">
-        <v>201.9301</v>
+        <v>201.9352</v>
       </c>
       <c r="D173" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E173" s="2" t="n">
-        <v>0.0604</v>
+        <v>0.0606</v>
       </c>
     </row>
     <row r="174">
@@ -3402,16 +3402,16 @@
         <v>744</v>
       </c>
       <c r="B174" s="2" t="n">
-        <v>16.5621</v>
+        <v>16.499</v>
       </c>
       <c r="C174" s="2" t="n">
-        <v>205.9866</v>
+        <v>205.9922</v>
       </c>
       <c r="D174" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E174" s="2" t="n">
-        <v>0.0604</v>
+        <v>0.0606</v>
       </c>
     </row>
     <row r="175">
@@ -3419,16 +3419,16 @@
         <v>746</v>
       </c>
       <c r="B175" s="2" t="n">
-        <v>16.5879</v>
+        <v>16.5206</v>
       </c>
       <c r="C175" s="2" t="n">
-        <v>210.0067</v>
+        <v>210.0129</v>
       </c>
       <c r="D175" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E175" s="2" t="n">
-        <v>0.0603</v>
+        <v>0.0606</v>
       </c>
     </row>
     <row r="176">
@@ -3436,16 +3436,16 @@
         <v>748</v>
       </c>
       <c r="B176" s="2" t="n">
-        <v>16.6099</v>
+        <v>16.5388</v>
       </c>
       <c r="C176" s="2" t="n">
-        <v>214.1753</v>
+        <v>214.183</v>
       </c>
       <c r="D176" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>0.0603</v>
+        <v>0.0605</v>
       </c>
     </row>
     <row r="177">
@@ -3453,16 +3453,16 @@
         <v>750</v>
       </c>
       <c r="B177" s="2" t="n">
-        <v>16.6304</v>
+        <v>16.5556</v>
       </c>
       <c r="C177" s="2" t="n">
-        <v>218.1682</v>
+        <v>218.1772</v>
       </c>
       <c r="D177" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E177" s="2" t="n">
-        <v>0.0602</v>
+        <v>0.0605</v>
       </c>
     </row>
     <row r="178">
@@ -3470,16 +3470,16 @@
         <v>752</v>
       </c>
       <c r="B178" s="2" t="n">
-        <v>16.6728</v>
+        <v>16.5947</v>
       </c>
       <c r="C178" s="2" t="n">
-        <v>222.4439</v>
+        <v>222.4559</v>
       </c>
       <c r="D178" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E178" s="2" t="n">
-        <v>0.0601</v>
+        <v>0.0604</v>
       </c>
     </row>
     <row r="179">
@@ -3487,16 +3487,16 @@
         <v>754</v>
       </c>
       <c r="B179" s="2" t="n">
-        <v>16.7229</v>
+        <v>16.6418</v>
       </c>
       <c r="C179" s="2" t="n">
-        <v>226.3357</v>
+        <v>226.3497</v>
       </c>
       <c r="D179" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E179" s="2" t="n">
-        <v>0.06</v>
+        <v>0.0602</v>
       </c>
     </row>
     <row r="180">
@@ -3504,16 +3504,16 @@
         <v>756</v>
       </c>
       <c r="B180" s="2" t="n">
-        <v>16.7503</v>
+        <v>16.6662</v>
       </c>
       <c r="C180" s="2" t="n">
-        <v>230.5625</v>
+        <v>230.5802</v>
       </c>
       <c r="D180" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E180" s="2" t="n">
-        <v>0.0598</v>
+        <v>0.0601</v>
       </c>
     </row>
     <row r="181">
@@ -3521,16 +3521,16 @@
         <v>758</v>
       </c>
       <c r="B181" s="2" t="n">
-        <v>16.8243</v>
+        <v>16.7372</v>
       </c>
       <c r="C181" s="2" t="n">
-        <v>234.5217</v>
+        <v>234.5424</v>
       </c>
       <c r="D181" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E181" s="2" t="n">
-        <v>0.0596</v>
+        <v>0.0599</v>
       </c>
     </row>
     <row r="182">
@@ -3538,16 +3538,16 @@
         <v>760</v>
       </c>
       <c r="B182" s="2" t="n">
-        <v>16.887</v>
+        <v>16.7965</v>
       </c>
       <c r="C182" s="2" t="n">
-        <v>238.7022</v>
+        <v>238.7271</v>
       </c>
       <c r="D182" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E182" s="2" t="n">
-        <v>0.0594</v>
+        <v>0.0597</v>
       </c>
     </row>
     <row r="183">
@@ -3555,16 +3555,16 @@
         <v>762</v>
       </c>
       <c r="B183" s="2" t="n">
-        <v>16.973</v>
+        <v>16.8786</v>
       </c>
       <c r="C183" s="2" t="n">
-        <v>242.7804</v>
+        <v>242.8097</v>
       </c>
       <c r="D183" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E183" s="2" t="n">
-        <v>0.0591</v>
+        <v>0.0594</v>
       </c>
     </row>
     <row r="184">
@@ -3572,16 +3572,16 @@
         <v>764</v>
       </c>
       <c r="B184" s="2" t="n">
-        <v>17.0696</v>
+        <v>16.9709</v>
       </c>
       <c r="C184" s="2" t="n">
-        <v>246.9787</v>
+        <v>247.0134</v>
       </c>
       <c r="D184" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E184" s="2" t="n">
-        <v>0.0588</v>
+        <v>0.0591</v>
       </c>
     </row>
     <row r="185">
@@ -3589,16 +3589,16 @@
         <v>766</v>
       </c>
       <c r="B185" s="2" t="n">
-        <v>17.2132</v>
+        <v>17.1099</v>
       </c>
       <c r="C185" s="2" t="n">
-        <v>251.1233</v>
+        <v>251.1634</v>
       </c>
       <c r="D185" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E185" s="2" t="n">
-        <v>0.0584</v>
+        <v>0.0587</v>
       </c>
     </row>
     <row r="186">
@@ -3606,16 +3606,16 @@
         <v>768</v>
       </c>
       <c r="B186" s="2" t="n">
-        <v>17.3782</v>
+        <v>17.2703</v>
       </c>
       <c r="C186" s="2" t="n">
-        <v>255.3245</v>
+        <v>255.3708</v>
       </c>
       <c r="D186" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E186" s="2" t="n">
-        <v>0.058</v>
+        <v>0.0583</v>
       </c>
     </row>
     <row r="187">
@@ -3623,16 +3623,16 @@
         <v>770</v>
       </c>
       <c r="B187" s="2" t="n">
-        <v>17.5196</v>
+        <v>17.4069</v>
       </c>
       <c r="C187" s="2" t="n">
-        <v>259.6274</v>
+        <v>259.6806</v>
       </c>
       <c r="D187" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E187" s="2" t="n">
-        <v>0.0575</v>
+        <v>0.0578</v>
       </c>
     </row>
     <row r="188">
@@ -3640,16 +3640,16 @@
         <v>772</v>
       </c>
       <c r="B188" s="2" t="n">
-        <v>17.7174</v>
+        <v>17.6001</v>
       </c>
       <c r="C188" s="2" t="n">
-        <v>264.0432</v>
+        <v>264.1037</v>
       </c>
       <c r="D188" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E188" s="2" t="n">
-        <v>0.057</v>
+        <v>0.0573</v>
       </c>
     </row>
     <row r="189">
@@ -3657,16 +3657,16 @@
         <v>774</v>
       </c>
       <c r="B189" s="2" t="n">
-        <v>17.8924</v>
+        <v>17.7704</v>
       </c>
       <c r="C189" s="2" t="n">
-        <v>268.278</v>
+        <v>268.3445</v>
       </c>
       <c r="D189" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E189" s="2" t="n">
-        <v>0.0564</v>
+        <v>0.0567</v>
       </c>
     </row>
     <row r="190">
@@ -3674,16 +3674,16 @@
         <v>776</v>
       </c>
       <c r="B190" s="2" t="n">
-        <v>18.1551</v>
+        <v>18.0282</v>
       </c>
       <c r="C190" s="2" t="n">
-        <v>272.8362</v>
+        <v>272.9104</v>
       </c>
       <c r="D190" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E190" s="2" t="n">
-        <v>0.0557</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="191">
@@ -3691,16 +3691,16 @@
         <v>778</v>
       </c>
       <c r="B191" s="2" t="n">
-        <v>18.426</v>
+        <v>18.2935</v>
       </c>
       <c r="C191" s="2" t="n">
-        <v>277.5004</v>
+        <v>277.5828</v>
       </c>
       <c r="D191" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E191" s="2" t="n">
-        <v>0.055</v>
+        <v>0.0553</v>
       </c>
     </row>
     <row r="192">
@@ -3708,16 +3708,16 @@
         <v>780</v>
       </c>
       <c r="B192" s="2" t="n">
-        <v>18.7798</v>
+        <v>18.6408</v>
       </c>
       <c r="C192" s="2" t="n">
-        <v>282.0481</v>
+        <v>282.138</v>
       </c>
       <c r="D192" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E192" s="2" t="n">
-        <v>0.0542</v>
+        <v>0.0546</v>
       </c>
     </row>
     <row r="193">
@@ -3725,16 +3725,16 @@
         <v>782</v>
       </c>
       <c r="B193" s="2" t="n">
-        <v>19.0892</v>
+        <v>18.9409</v>
       </c>
       <c r="C193" s="2" t="n">
-        <v>286.8382</v>
+        <v>286.9382</v>
       </c>
       <c r="D193" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E193" s="2" t="n">
-        <v>0.0534</v>
+        <v>0.0538</v>
       </c>
     </row>
     <row r="194">
@@ -3742,16 +3742,16 @@
         <v>784</v>
       </c>
       <c r="B194" s="2" t="n">
-        <v>19.4409</v>
+        <v>19.282</v>
       </c>
       <c r="C194" s="2" t="n">
-        <v>291.6724</v>
+        <v>291.7824</v>
       </c>
       <c r="D194" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E194" s="2" t="n">
-        <v>0.0526</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="195">
@@ -3759,16 +3759,16 @@
         <v>786</v>
       </c>
       <c r="B195" s="2" t="n">
-        <v>19.8327</v>
+        <v>19.6622</v>
       </c>
       <c r="C195" s="2" t="n">
-        <v>296.7134</v>
+        <v>296.8332</v>
       </c>
       <c r="D195" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E195" s="2" t="n">
-        <v>0.0517</v>
+        <v>0.0521</v>
       </c>
     </row>
     <row r="196">
@@ -3776,16 +3776,16 @@
         <v>788</v>
       </c>
       <c r="B196" s="2" t="n">
-        <v>20.2256</v>
+        <v>20.0422</v>
       </c>
       <c r="C196" s="2" t="n">
-        <v>301.8813</v>
+        <v>302.0094</v>
       </c>
       <c r="D196" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E196" s="2" t="n">
-        <v>0.0509</v>
+        <v>0.0512</v>
       </c>
     </row>
     <row r="197">
@@ -3793,16 +3793,16 @@
         <v>790</v>
       </c>
       <c r="B197" s="2" t="n">
-        <v>20.6595</v>
+        <v>20.4621</v>
       </c>
       <c r="C197" s="2" t="n">
-        <v>307.2947</v>
+        <v>307.4294</v>
       </c>
       <c r="D197" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E197" s="2" t="n">
-        <v>0.05</v>
+        <v>0.0504</v>
       </c>
     </row>
     <row r="198">
@@ -3810,16 +3810,16 @@
         <v>792</v>
       </c>
       <c r="B198" s="2" t="n">
-        <v>21.1113</v>
+        <v>20.8984</v>
       </c>
       <c r="C198" s="2" t="n">
-        <v>312.8514</v>
+        <v>312.9893</v>
       </c>
       <c r="D198" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E198" s="2" t="n">
-        <v>0.0491</v>
+        <v>0.0495</v>
       </c>
     </row>
     <row r="199">
@@ -3827,16 +3827,16 @@
         <v>794</v>
       </c>
       <c r="B199" s="2" t="n">
-        <v>21.5432</v>
+        <v>21.3137</v>
       </c>
       <c r="C199" s="2" t="n">
-        <v>318.6677</v>
+        <v>318.8057</v>
       </c>
       <c r="D199" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E199" s="2" t="n">
-        <v>0.0483</v>
+        <v>0.0488</v>
       </c>
     </row>
     <row r="200">
@@ -3844,16 +3844,16 @@
         <v>796</v>
       </c>
       <c r="B200" s="2" t="n">
-        <v>21.9667</v>
+        <v>21.7202</v>
       </c>
       <c r="C200" s="2" t="n">
-        <v>324.68</v>
+        <v>324.8136</v>
       </c>
       <c r="D200" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E200" s="2" t="n">
-        <v>0.0476</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="201">
@@ -3861,16 +3861,16 @@
         <v>798</v>
       </c>
       <c r="B201" s="2" t="n">
-        <v>22.3546</v>
+        <v>22.0917</v>
       </c>
       <c r="C201" s="2" t="n">
-        <v>330.8535</v>
+        <v>330.9773</v>
       </c>
       <c r="D201" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E201" s="2" t="n">
-        <v>0.047</v>
+        <v>0.0474</v>
       </c>
     </row>
     <row r="202">
@@ -3878,16 +3878,16 @@
         <v>800</v>
       </c>
       <c r="B202" s="2" t="n">
-        <v>22.6826</v>
+        <v>22.4047</v>
       </c>
       <c r="C202" s="2" t="n">
-        <v>337.197</v>
+        <v>337.3059</v>
       </c>
       <c r="D202" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E202" s="2" t="n">
-        <v>0.0464</v>
+        <v>0.0469</v>
       </c>
     </row>
   </sheetData>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Кремний c-Si (табличные n, k); задней стороны нет (полубесконечная)</t>
+          <t>Кремний c-Si (Green 2008, 250–1450 нм); задней стороны нет (полубесконечная)</t>
         </is>
       </c>
     </row>
